--- a/output/full_scan/batch_seq7_2026-09-16.xlsx
+++ b/output/full_scan/batch_seq7_2026-09-16.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6683</v>
+        <v>6538</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>753.7239782630385</v>
+        <v>807.1793498944101</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1595</v>
+        <v>380.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>66.10158146356589</v>
+        <v>83.54820305861431</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14.63579075713385</v>
+        <v>60.68919499161305</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.201162553511629</v>
+        <v>0.1964256292399496</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>24.54114716786892</v>
+        <v>9.555868541639979</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6560</v>
+        <v>6683</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>737.1937796170207</v>
+        <v>753.7239782630385</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35</v>
+        <v>1595</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>58.06253068918653</v>
+        <v>66.10158146356589</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10.74090961941571</v>
+        <v>14.63579075713385</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5.079188489366453</v>
+        <v>2.201162553511629</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.5444489953146472</v>
+        <v>24.54114716786892</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6668</v>
+        <v>6560</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>735.1810887972071</v>
+        <v>737.1937796170207</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>43.2</v>
+        <v>35</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.86255146133936</v>
+        <v>58.06253068918653</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>37.13290795861492</v>
+        <v>10.74090961941571</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.8181088797207</v>
+        <v>5.079188489366453</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.0208200482905906</v>
+        <v>0.5444489953146472</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6716</v>
+        <v>6668</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>665.4512024765146</v>
+        <v>735.1810887972071</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>118.5</v>
+        <v>43.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>51.42996026109227</v>
+        <v>59.86255146133936</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>27.75405545981616</v>
+        <v>37.13290795861492</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3964051679302451</v>
+        <v>1.8181088797207</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-2.051031513054144</v>
+        <v>-0.0208200482905906</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6742</v>
+        <v>6716</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>635.0375652189612</v>
+        <v>665.4512024765146</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46.6</v>
+        <v>118.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.18836069414247</v>
+        <v>51.42996026109227</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25.59018151902165</v>
+        <v>27.75405545981616</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.140568682790185</v>
+        <v>0.3964051679302451</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.3183302507860536</v>
+        <v>-2.051031513054144</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, williams_r_recovery, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6706</v>
+        <v>6742</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>633.759679263385</v>
+        <v>635.0375652189612</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>147</v>
+        <v>46.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>65.86929025140063</v>
+        <v>55.18836069414247</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28.80380223805584</v>
+        <v>25.59018151902165</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.6759679263385</v>
+        <v>1.140568682790185</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.795250630018722</v>
+        <v>0.3183302507860536</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, williams_r_recovery, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6771</v>
+        <v>6706</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>627.6820153648447</v>
+        <v>633.759679263385</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>42.2</v>
+        <v>147</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.06984573400427</v>
+        <v>65.86929025140063</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.25962896199369</v>
+        <v>28.80380223805584</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.570904918068449</v>
+        <v>2.6759679263385</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.09012157326375821</v>
+        <v>2.795250630018722</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6510</v>
+        <v>6771</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>623.8376374222242</v>
+        <v>627.6820153648447</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3230</v>
+        <v>42.2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>53.17443291224029</v>
+        <v>61.06984573400427</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>33.1828499277719</v>
+        <v>24.25962896199369</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.7545152274414409</v>
+        <v>2.570904918068449</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.4725927375916683</v>
+        <v>-0.09012157326375821</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6727</v>
+        <v>6510</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>623.1937604180446</v>
+        <v>623.8376374222242</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>477</v>
+        <v>3230</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>48.18545218584557</v>
+        <v>53.17443291224029</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>22.69193997711245</v>
+        <v>33.1828499277719</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.3600735983398031</v>
+        <v>0.7545152274414409</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-10.78637206269691</v>
+        <v>-0.4725927375916683</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6532</v>
+        <v>6727</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>616.8213149451824</v>
+        <v>623.1937604180446</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>92</v>
+        <v>477</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>51.87706334553936</v>
+        <v>48.18545218584557</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37.98037408957134</v>
+        <v>22.69193997711245</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.3628508549766971</v>
+        <v>0.3600735983398031</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1.062151253355214</v>
+        <v>-10.78637206269691</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6782</v>
+        <v>6532</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>613.0305733585568</v>
+        <v>616.8213149451824</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>231.5</v>
+        <v>92</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>55.93013832441354</v>
+        <v>51.87706334553936</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.95109246315297</v>
+        <v>37.98037408957134</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.2849437462452104</v>
+        <v>0.3628508549766971</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.933711798618196</v>
+        <v>-1.062151253355214</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6654</v>
+        <v>6782</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>610.4057082071372</v>
+        <v>613.0305733585568</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>202</v>
+        <v>231.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.81037633834633</v>
+        <v>55.93013832441354</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>25.75779734700999</v>
+        <v>21.95109246315297</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.2801887319695205</v>
+        <v>0.2849437462452104</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.4764387814367907</v>
+        <v>-1.933711798618196</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6830</v>
+        <v>6654</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>602.3495811517329</v>
+        <v>610.4057082071372</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>529</v>
+        <v>202</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>52.3034624461627</v>
+        <v>55.81037633834633</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>33.40590244882703</v>
+        <v>25.75779734700999</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6121321094034288</v>
+        <v>0.2801887319695205</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-7.132167976259254</v>
+        <v>-0.4764387814367907</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6684</v>
+        <v>6830</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>601.0901351583433</v>
+        <v>602.3495811517329</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46.85</v>
+        <v>529</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>51.50884134709685</v>
+        <v>52.3034624461627</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>8.499512312777115</v>
+        <v>33.40590244882703</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.0846737911953</v>
+        <v>0.6121321094034288</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0735152161317815</v>
+        <v>-7.132167976259254</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6588</v>
+        <v>6684</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>597.0975175074535</v>
+        <v>601.0901351583433</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>110</v>
+        <v>46.85</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.5249784335406</v>
+        <v>51.50884134709685</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.36730910513868</v>
+        <v>8.499512312777115</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3939147117831709</v>
+        <v>2.0846737911953</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-1.198017749643825</v>
+        <v>0.0735152161317815</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6505</v>
+        <v>6588</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>595.0823240911714</v>
+        <v>597.0975175074535</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>80.5</v>
+        <v>110</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.00673662891243</v>
+        <v>54.5249784335406</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>39.27213181397296</v>
+        <v>25.36730910513868</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.9413724689576296</v>
+        <v>0.3939147117831709</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3009203706884733</v>
+        <v>-1.198017749643825</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6691</v>
+        <v>6505</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>593.5443401199401</v>
+        <v>595.0823240911714</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>618</v>
+        <v>80.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>43.60772057267765</v>
+        <v>56.00673662891243</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>20.49622193191869</v>
+        <v>39.27213181397296</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.9540059169915548</v>
+        <v>0.9413724689576296</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.361083458285645</v>
+        <v>0.3009203706884733</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6491</v>
+        <v>6691</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>571.3418022180613</v>
+        <v>593.5443401199401</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>393</v>
+        <v>618</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.92229131436281</v>
+        <v>43.60772057267765</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.77479975959853</v>
+        <v>20.49622193191869</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.9758436481124364</v>
+        <v>0.9540059169915548</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.2990811790978158</v>
+        <v>2.361083458285645</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6657</v>
+        <v>6491</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>555.7735829985203</v>
+        <v>571.3418022180613</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>33.85</v>
+        <v>393</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.05741698285799</v>
+        <v>60.92229131436281</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>25.68125649656901</v>
+        <v>23.77479975959853</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5151324568588959</v>
+        <v>0.9758436481124364</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.4168420563950397</v>
+        <v>-0.2990811790978158</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6805</v>
+        <v>6657</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>551.5603959934045</v>
+        <v>555.7735829985203</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2045</v>
+        <v>33.85</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.04649991968024</v>
+        <v>56.05741698285799</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25.69618936912202</v>
+        <v>25.68125649656901</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.64953713326152</v>
+        <v>0.5151324568588959</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-34.09415460843709</v>
+        <v>0.4168420563950397</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6584</v>
+        <v>6805</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>541.6342788873928</v>
+        <v>551.5603959934045</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>555</v>
+        <v>2045</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>43.93366084531771</v>
+        <v>51.04649991968024</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>22.16254429676288</v>
+        <v>25.69618936912202</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2664904034001984</v>
+        <v>0.64953713326152</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-11.10144533190896</v>
+        <v>-34.09415460843709</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6651</v>
+        <v>6584</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>537.3164394495803</v>
+        <v>541.6342788873928</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>145</v>
+        <v>555</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.55340891830621</v>
+        <v>43.93366084531771</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>21.67370889860591</v>
+        <v>22.16254429676288</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4704514219262078</v>
+        <v>0.2664904034001984</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-1.10110979372684</v>
+        <v>-11.10144533190896</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6743</v>
+        <v>6651</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>533.9894291297431</v>
+        <v>537.3164394495803</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>29.15</v>
+        <v>145</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.6980152609753</v>
+        <v>53.55340891830621</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.87740475878633</v>
+        <v>21.67370889860591</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.244495179016016</v>
+        <v>0.4704514219262078</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.215614151829898</v>
+        <v>-1.10110979372684</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6486</v>
+        <v>6743</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>533.6296382828621</v>
+        <v>533.9894291297431</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>29.15</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>59.51863834331893</v>
+        <v>59.6980152609753</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>42.97707891788534</v>
+        <v>23.87740475878633</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2529446703000251</v>
+        <v>1.244495179016016</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0610226929596142</v>
+        <v>0.215614151829898</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6568</v>
+        <v>6486</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>532.3715846173786</v>
+        <v>533.6296382828621</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>135.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.70668708133316</v>
+        <v>59.51863834331893</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>20.66896150805842</v>
+        <v>42.97707891788534</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.152418311105489</v>
+        <v>0.2529446703000251</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>1</v>
@@ -2001,51 +2001,51 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.7004826558389057</v>
+        <v>0.0610226929596142</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6806</v>
+        <v>6568</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>532.3715846173786</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>3.51</v>
+        <v>135.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>31.69503023882532</v>
+        <v>50.70668708133316</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>32.59322745894141</v>
+        <v>20.66896150805842</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>2.152418311105489</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.4112821060521474</v>
+        <v>0.7004826558389057</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2064,38 +2064,38 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6666</v>
+        <v>6806</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>521.9470410916182</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>44.35</v>
+        <v>3.51</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>52.48682396603337</v>
+        <v>31.69503023882532</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>12.22470425208982</v>
+        <v>32.59322745894141</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8026128259248998</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.044903930012897</v>
+        <v>0.4112821060521474</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6834</v>
+        <v>6666</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>520.2412786693843</v>
+        <v>521.9470410916182</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>100</v>
+        <v>44.35</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.45756032536196</v>
+        <v>52.48682396603337</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18.50310510993405</v>
+        <v>12.22470425208982</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6304976790929806</v>
+        <v>0.8026128259248998</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.8166793319076683</v>
+        <v>-0.044903930012897</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6640</v>
+        <v>6834</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>517.8385961598576</v>
+        <v>520.2412786693843</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1115</v>
+        <v>100</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>50.84744711320659</v>
+        <v>53.45756032536196</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>26.24771033975213</v>
+        <v>18.50310510993405</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2227729777729597</v>
+        <v>0.6304976790929806</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-11.25159943413215</v>
+        <v>0.8166793319076683</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6715</v>
+        <v>6640</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>507.5885445424463</v>
+        <v>517.8385961598576</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>393</v>
+        <v>1115</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.94928158648837</v>
+        <v>50.84744711320659</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11.04892995500581</v>
+        <v>26.24771033975213</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.358854454244632</v>
+        <v>0.2227729777729597</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>5.036621327479665</v>
+        <v>-11.25159943413215</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6667</v>
+        <v>6715</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>498.6858603310415</v>
+        <v>507.5885445424463</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>236.5</v>
+        <v>393</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.26382342001144</v>
+        <v>55.94928158648837</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>32.77633880509732</v>
+        <v>11.04892995500581</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4533277954394453</v>
+        <v>2.358854454244632</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.475128576876517</v>
+        <v>5.036621327479665</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6807</v>
+        <v>6667</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>474.2444373292539</v>
+        <v>498.6858603310415</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>33</v>
+        <v>236.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>50.57729774443513</v>
+        <v>51.26382342001144</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.39536591762142</v>
+        <v>32.77633880509732</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.1193809387332172</v>
+        <v>0.4533277954394453</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1098975126265167</v>
+        <v>1.475128576876517</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6725</v>
+        <v>6807</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>471.8061474957717</v>
+        <v>474.2444373292539</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>207.5</v>
+        <v>33</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>33.54695663903766</v>
+        <v>50.57729774443513</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>33.0752328857676</v>
+        <v>20.39536591762142</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4069616765942841</v>
+        <v>0.1193809387332172</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0455038291604417</v>
+        <v>0.1098975126265167</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, dealer_buy_3d</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6579</v>
+        <v>6725</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>453.2781599362379</v>
+        <v>471.8061474957717</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>149</v>
+        <v>207.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>47.08185492323705</v>
+        <v>33.54695663903766</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>21.33384322461533</v>
+        <v>33.0752328857676</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5602927221465829</v>
+        <v>0.4069616765942841</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.5965743309547946</v>
+        <v>0.0455038291604417</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6664</v>
+        <v>6579</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>450.4414741253197</v>
+        <v>453.2781599362379</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>336</v>
+        <v>149</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>42.52415578754611</v>
+        <v>47.08185492323705</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>11.75985369808842</v>
+        <v>21.33384322461533</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2725200538897064</v>
+        <v>0.5602927221465829</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-2.263701727437565</v>
+        <v>0.5965743309547946</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6670</v>
+        <v>6664</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>449.7716116911431</v>
+        <v>450.4414741253197</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>270</v>
+        <v>336</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>47.84109807086339</v>
+        <v>42.52415578754611</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>28.46626036136663</v>
+        <v>11.75985369808842</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4404976460883897</v>
+        <v>0.2725200538897064</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.010962696912912</v>
+        <v>-2.263701727437565</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6761</v>
+        <v>6670</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>443.2646499867405</v>
+        <v>449.7716116911431</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>163.5</v>
+        <v>270</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>40.16028623860774</v>
+        <v>47.84109807086339</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.06051061066296</v>
+        <v>28.46626036136663</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.1363957295729534</v>
+        <v>0.4404976460883897</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-3.131661011219542</v>
+        <v>-1.010962696912912</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6642</v>
+        <v>6761</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>437.5520202434687</v>
+        <v>443.2646499867405</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>75.8</v>
+        <v>163.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>43.4190204676655</v>
+        <v>40.16028623860774</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.5946617195058</v>
+        <v>20.06051061066296</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.1701090647819666</v>
+        <v>0.1363957295729534</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.6151741737970913</v>
+        <v>-3.131661011219542</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6693</v>
+        <v>6642</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>435.607135191143</v>
+        <v>437.5520202434687</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>184</v>
+        <v>75.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.58627766811286</v>
+        <v>43.4190204676655</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>14.46943647480423</v>
+        <v>13.5946617195058</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.23515078108102</v>
+        <v>0.1701090647819666</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.6605227019301798</v>
+        <v>-0.6151741737970913</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6531</v>
+        <v>6693</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>432.3136714157415</v>
+        <v>435.607135191143</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>949</v>
+        <v>184</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.64557302871718</v>
+        <v>53.58627766811286</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12.70730439663184</v>
+        <v>14.46943647480423</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8509445303751048</v>
+        <v>1.23515078108102</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.871430039188769</v>
+        <v>0.6605227019301798</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6613</v>
+        <v>6531</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>428.3665049084579</v>
+        <v>432.3136714157415</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>264</v>
+        <v>949</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.16979135520946</v>
+        <v>52.64557302871718</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>8.281969554404283</v>
+        <v>12.70730439663184</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3621926077201619</v>
+        <v>0.8509445303751048</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.212407803382084</v>
+        <v>-1.871430039188769</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6789</v>
+        <v>6613</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>426.2653272776839</v>
+        <v>428.3665049084579</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>434</v>
+        <v>264</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>43.41234577214765</v>
+        <v>48.16979135520946</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>14.46470991656834</v>
+        <v>8.281969554404283</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6983103006558407</v>
+        <v>0.3621926077201619</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-3.535441570435985</v>
+        <v>1.212407803382084</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6722</v>
+        <v>6789</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>421.1191312830102</v>
+        <v>426.2653272776839</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>32.5</v>
+        <v>434</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45.47468732233574</v>
+        <v>43.41234577214765</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.98713206480576</v>
+        <v>14.46470991656834</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.9748375071688014</v>
+        <v>0.6983103006558407</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>5.295716539652218e-05</v>
+        <v>-3.535441570435985</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6643</v>
+        <v>6722</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>420.2178891815963</v>
+        <v>421.1191312830102</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>420</v>
+        <v>32.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.239710215906</v>
+        <v>45.47468732233574</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11.38850466210156</v>
+        <v>17.98713206480576</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4863345591648021</v>
+        <v>0.9748375071688014</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.402331407655196</v>
+        <v>5.295716539652218e-05</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6658</v>
+        <v>6643</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>413.8237345033632</v>
+        <v>420.2178891815963</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>167.5</v>
+        <v>420</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.34508754227084</v>
+        <v>49.239710215906</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.67380314873713</v>
+        <v>11.38850466210156</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.52898778778029</v>
+        <v>0.4863345591648021</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-1.050033321275875</v>
+        <v>0.402331407655196</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6689</v>
+        <v>6658</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>411.2936758593743</v>
+        <v>413.8237345033632</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>67</v>
+        <v>167.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>59.73309013461109</v>
+        <v>49.34508754227084</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.57469411990101</v>
+        <v>13.67380314873713</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3.229367585937431</v>
+        <v>0.52898778778029</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.8221705885034005</v>
+        <v>-1.050033321275875</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6690</v>
+        <v>6689</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>404.3668660082743</v>
+        <v>411.2936758593743</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>67.16053458152719</v>
+        <v>59.73309013461109</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.22392003416831</v>
+        <v>19.57469411990101</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.33668660082743</v>
+        <v>3.229367585937431</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.348073301244207</v>
+        <v>0.8221705885034005</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6655</v>
+        <v>6690</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>400.254401271789</v>
+        <v>404.3668660082743</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.1764012155073</v>
+        <v>67.16053458152719</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11.3559645326409</v>
+        <v>22.22392003416831</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.1254401271789012</v>
+        <v>3.33668660082743</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.450079352328418</v>
+        <v>2.348073301244207</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6570</v>
+        <v>6655</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>398.9505546698417</v>
+        <v>400.254401271789</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>33.98926623403365</v>
+        <v>53.1764012155073</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24.99841424922995</v>
+        <v>11.3559645326409</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2362602131995052</v>
+        <v>0.1254401271789012</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.4951178832919454</v>
+        <v>2.450079352328418</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6581</v>
+        <v>6570</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>397.272526870223</v>
+        <v>398.9505546698417</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>109.5</v>
+        <v>47</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.37352079325379</v>
+        <v>33.98926623403365</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23.6636811386408</v>
+        <v>24.99841424922995</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7020742559214036</v>
+        <v>0.2362602131995052</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0063358668015529</v>
+        <v>-0.4951178832919454</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6585</v>
+        <v>6581</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>396.8457437270076</v>
+        <v>397.272526870223</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>103</v>
+        <v>109.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>32.71316611400921</v>
+        <v>51.37352079325379</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>28.49927240914919</v>
+        <v>23.6636811386408</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.978532582644372</v>
+        <v>0.7020742559214036</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.8609876713167579</v>
+        <v>-0.0063358668015529</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6770</v>
+        <v>6585</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>391.3960294936461</v>
+        <v>396.8457437270076</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>103</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.19333149491931</v>
+        <v>32.71316611400921</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>9.706169092376758</v>
+        <v>28.49927240914919</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6715305546388511</v>
+        <v>0.978532582644372</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.334550660174004</v>
+        <v>-0.8609876713167579</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6533</v>
+        <v>6770</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>387.2198904342992</v>
+        <v>391.3960294936461</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>229</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>37.75077494306995</v>
+        <v>50.19333149491931</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.12059208579876</v>
+        <v>9.706169092376758</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3672532651127921</v>
+        <v>0.6715305546388511</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-5.304922503566218</v>
+        <v>-0.334550660174004</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6674</v>
+        <v>6533</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>386.8433982538983</v>
+        <v>387.2198904342992</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>15.95</v>
+        <v>229</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.07693988538991</v>
+        <v>37.75077494306995</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.06433382179862</v>
+        <v>18.12059208579876</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.0555261850469432</v>
+        <v>0.3672532651127921</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0105276997380184</v>
+        <v>-5.304922503566218</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6669</v>
+        <v>6674</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>372.6156177037915</v>
+        <v>386.8433982538983</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2165</v>
+        <v>15.95</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>25.56995722294192</v>
+        <v>51.07693988538991</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>41.72602342662846</v>
+        <v>24.06433382179862</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.661561770379152</v>
+        <v>0.0555261850469432</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-240.0784536031426</v>
+        <v>-0.0105276997380184</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6606</v>
+        <v>6669</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>372.0693494826047</v>
+        <v>372.6156177037915</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>24.7</v>
+        <v>2165</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>35.01108547978954</v>
+        <v>25.56995722294192</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15.05670747597477</v>
+        <v>41.72602342662846</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.553732043353064</v>
+        <v>2.661561770379152</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0957770091452147</v>
+        <v>-240.0784536031426</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6831</v>
+        <v>6606</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>370.8827624549521</v>
+        <v>372.0693494826047</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>525</v>
+        <v>24.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.04969408932133</v>
+        <v>35.01108547978954</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.23552279895979</v>
+        <v>15.05670747597477</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3704602018496835</v>
+        <v>1.553732043353064</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-5.054196600053778</v>
+        <v>-0.0957770091452147</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6829</v>
+        <v>6831</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>366.0773633068512</v>
+        <v>370.8827624549521</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>212.5</v>
+        <v>525</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.94010086242709</v>
+        <v>39.04969408932133</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.76436587462042</v>
+        <v>16.23552279895979</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5420874812769068</v>
+        <v>0.3704602018496835</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-4.972240391856539</v>
+        <v>-5.054196600053778</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6753</v>
+        <v>6829</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>353.4662886010628</v>
+        <v>366.0773633068512</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>132.5</v>
+        <v>212.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>42.47656606571795</v>
+        <v>44.94010086242709</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.05094701438592</v>
+        <v>18.76436587462042</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2292383578527267</v>
+        <v>0.5420874812769068</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.934301709970172</v>
+        <v>-4.972240391856539</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6517</v>
+        <v>6753</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>351.9240117298097</v>
+        <v>353.4662886010628</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>62.8</v>
+        <v>132.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.55628758282961</v>
+        <v>42.47656606571795</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.68324740359243</v>
+        <v>15.05094701438592</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4020887483544646</v>
+        <v>0.2292383578527267</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.8274846896651903</v>
+        <v>-0.934301709970172</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6799</v>
+        <v>6517</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>351.332281576554</v>
+        <v>351.9240117298097</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>42.97976691792789</v>
+        <v>43.55628758282961</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>11.16422521978104</v>
+        <v>14.68324740359243</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7344987122097004</v>
+        <v>0.4020887483544646</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0116983799304584</v>
+        <v>-0.8274846896651903</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6719</v>
+        <v>6799</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>333.7307198536898</v>
+        <v>351.332281576554</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>180.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>36.47410952432946</v>
+        <v>42.97976691792789</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>26.2488184473338</v>
+        <v>11.16422521978104</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3903428234557394</v>
+        <v>0.7344987122097004</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3479972293485787</v>
+        <v>0.0116983799304584</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6515</v>
+        <v>6719</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>333.4541393921985</v>
+        <v>333.7307198536898</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>6210</v>
+        <v>180.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>41.06856295221978</v>
+        <v>36.47410952432946</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16.59502272203894</v>
+        <v>26.2488184473338</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6676661058295904</v>
+        <v>0.3903428234557394</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-47.35415225835803</v>
+        <v>0.3479972293485787</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6558</v>
+        <v>6515</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>332.8625088328806</v>
+        <v>333.4541393921985</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>23.45</v>
+        <v>6210</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>39.08191616155929</v>
+        <v>41.06856295221978</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>30.72078113537498</v>
+        <v>16.59502272203894</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4139020667577763</v>
+        <v>0.6676661058295904</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0525698011451427</v>
+        <v>-47.35415225835803</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6526</v>
+        <v>6558</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>329.4563658735457</v>
+        <v>332.8625088328806</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>629</v>
+        <v>23.45</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>52.6301980749914</v>
+        <v>39.08191616155929</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.07011083801188</v>
+        <v>30.72078113537498</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7912780255924801</v>
+        <v>0.4139020667577763</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.6097349032491124</v>
+        <v>-0.0525698011451427</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6541</v>
+        <v>6526</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>325.9891129561444</v>
+        <v>329.4563658735457</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>30.55</v>
+        <v>629</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>26.75858381109716</v>
+        <v>52.6301980749914</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>33.87968883591891</v>
+        <v>15.07011083801188</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5622848701471714</v>
+        <v>0.7912780255924801</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.1327016272821279</v>
+        <v>-0.6097349032491124</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6548</v>
+        <v>6541</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>321.7074989669599</v>
+        <v>325.9891129561444</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>30.55</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.39473455406715</v>
+        <v>26.75858381109716</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>9.658632946016466</v>
+        <v>33.87968883591891</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4280081091595874</v>
+        <v>0.5622848701471714</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0347524769888386</v>
+        <v>-0.1327016272821279</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6597</v>
+        <v>6548</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>315.3440674530186</v>
+        <v>321.7074989669599</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.70792278514801</v>
+        <v>48.39473455406715</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7.736341454985022</v>
+        <v>9.658632946016466</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.2767165502247926</v>
+        <v>0.4280081091595874</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-2.11867003380498</v>
+        <v>-0.0347524769888386</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6504</v>
+        <v>6597</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>313.6772084573334</v>
+        <v>315.3440674530186</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>36.6</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>41.87507454551916</v>
+        <v>52.70792278514801</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.59553771320354</v>
+        <v>7.736341454985022</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.361690417444548</v>
+        <v>0.2767165502247926</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.1055285031835327</v>
+        <v>-2.11867003380498</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6692</v>
+        <v>6504</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>308.5944412116103</v>
+        <v>313.6772084573334</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>23.1</v>
+        <v>36.6</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.10929772254941</v>
+        <v>41.87507454551916</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>11.87448224301696</v>
+        <v>19.59553771320354</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4812990879148721</v>
+        <v>1.361690417444548</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.9194406400437812</v>
+        <v>-0.1055285031835327</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6756</v>
+        <v>6692</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>305.8990483030973</v>
+        <v>308.5944412116103</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>23.1</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.15629881898194</v>
+        <v>51.10929772254941</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11.14015945523955</v>
+        <v>11.87448224301696</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6343494722321839</v>
+        <v>0.4812990879148721</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.8100563471287485</v>
+        <v>-0.9194406400437812</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6488</v>
+        <v>6756</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>300.3694771422663</v>
+        <v>305.8990483030973</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>937</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,49 +4474,49 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.70907114536576</v>
+        <v>44.15629881898194</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7.644159943077637</v>
+        <v>11.14015945523955</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7708479943167545</v>
+        <v>0.6343494722321839</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-1.585991271542461</v>
+        <v>-0.8100563471287485</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6788</v>
+        <v>6488</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>298.9338875564442</v>
+        <v>300.3694771422663</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>326.5</v>
+        <v>937</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,49 +4527,49 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>38.42310588225585</v>
+        <v>47.70907114536576</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.12232325764714</v>
+        <v>7.644159943077637</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3049854390757982</v>
+        <v>0.7708479943167545</v>
       </c>
       <c r="K77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M77" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-3.695241642945244</v>
+        <v>-1.585991271542461</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6781</v>
+        <v>6788</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>296.11131868386</v>
+        <v>298.9338875564442</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1005</v>
+        <v>326.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.37701737869199</v>
+        <v>38.42310588225585</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>12.76573367220183</v>
+        <v>18.12232325764714</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4218217307901888</v>
+        <v>0.3049854390757982</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-12.88033677839562</v>
+        <v>-3.695241642945244</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4608,21 +4608,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6680</v>
+        <v>6781</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>288.4263936145271</v>
+        <v>296.11131868386</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>53.9</v>
+        <v>1005</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.32131204539685</v>
+        <v>42.37701737869199</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7.081196566977486</v>
+        <v>12.76573367220183</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.364934423355803</v>
+        <v>0.4218217307901888</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>2.315073003824761</v>
+        <v>-12.88033677839562</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6735</v>
+        <v>6680</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>287.8590003083516</v>
+        <v>288.4263936145271</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>61.3</v>
+        <v>53.9</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>43.69163379169077</v>
+        <v>52.32131204539685</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15.32511367784268</v>
+        <v>7.081196566977486</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5676524201984847</v>
+        <v>0.364934423355803</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0673367101596678</v>
+        <v>2.315073003824761</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6598</v>
+        <v>6735</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>286.9667742927465</v>
+        <v>287.8590003083516</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>27.4</v>
+        <v>61.3</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.41730323148605</v>
+        <v>43.69163379169077</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.32881401652435</v>
+        <v>15.32511367784268</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2154429016727743</v>
+        <v>0.5676524201984847</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1022736315334514</v>
+        <v>0.0673367101596678</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6577</v>
+        <v>6598</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>284.897764453135</v>
+        <v>286.9667742927465</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>79.7</v>
+        <v>27.4</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,49 +4792,49 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>49.71939884412944</v>
+        <v>46.41730323148605</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>12.69442950013885</v>
+        <v>17.32881401652435</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4291042155837556</v>
+        <v>0.2154429016727743</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1056243709515887</v>
+        <v>-0.1022736315334514</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6624</v>
+        <v>6577</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>283.0757914066587</v>
+        <v>284.897764453135</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>38.85</v>
+        <v>79.7</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,49 +4845,49 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>52.08959672086299</v>
+        <v>49.71939884412944</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>7.619973445189688</v>
+        <v>12.69442950013885</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.827816448321631</v>
+        <v>0.4291042155837556</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M83" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>1.05759288656307</v>
+        <v>-0.1056243709515887</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6573</v>
+        <v>6624</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>271.4626199045746</v>
+        <v>283.0757914066587</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>16.2</v>
+        <v>38.85</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>44.62039914283962</v>
+        <v>52.08959672086299</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.04097486222839</v>
+        <v>7.619973445189688</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.3515410616942433</v>
+        <v>1.827816448321631</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0433944356311875</v>
+        <v>1.05759288656307</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6739</v>
+        <v>6573</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>268.8316163216142</v>
+        <v>271.4626199045746</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1050</v>
+        <v>16.2</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45.99026195399843</v>
+        <v>44.62039914283962</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15.14022617509032</v>
+        <v>16.04097486222839</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7831616321614188</v>
+        <v>0.3515410616942433</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-5.772404618686576</v>
+        <v>-0.0433944356311875</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6754</v>
+        <v>6739</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>266.9335514990726</v>
+        <v>268.8316163216142</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>40.9</v>
+        <v>1050</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>36.91163898330139</v>
+        <v>45.99026195399843</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12.45120330280594</v>
+        <v>15.14022617509032</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>2.042152482124139</v>
+        <v>0.7831616321614188</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.08557899989701841</v>
+        <v>-5.772404618686576</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6525</v>
+        <v>6754</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>264.4091765518628</v>
+        <v>266.9335514990726</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>128.5</v>
+        <v>40.9</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>42.0824931396666</v>
+        <v>36.91163898330139</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.49234980977448</v>
+        <v>12.45120330280594</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.7393447126050254</v>
+        <v>2.042152482124139</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.7958074286278256</v>
+        <v>-0.08557899989701841</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6679</v>
+        <v>6525</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>258.7147046984942</v>
+        <v>264.4091765518628</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>197.5</v>
+        <v>128.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>42.67317817417167</v>
+        <v>42.0824931396666</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.60931082055948</v>
+        <v>15.49234980977448</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2426119542934716</v>
+        <v>0.7393447126050254</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.2721900147421552</v>
+        <v>-0.7958074286278256</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6796</v>
+        <v>6679</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>255.5331805175822</v>
+        <v>258.7147046984942</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>50.2</v>
+        <v>197.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>26.37291410032884</v>
+        <v>42.67317817417167</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>25.37743854058354</v>
+        <v>15.60931082055948</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.4533180517582178</v>
+        <v>0.2426119542934716</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-1.170764239846648</v>
+        <v>0.2721900147421552</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6645</v>
+        <v>6796</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>255.2783363034538</v>
+        <v>255.5331805175822</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>12.65</v>
+        <v>50.2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.21060650002418</v>
+        <v>26.37291410032884</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>29.50406548288369</v>
+        <v>25.37743854058354</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.216997632070322</v>
+        <v>0.4533180517582178</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0822550094043432</v>
+        <v>-1.170764239846648</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5244,21 +5244,21 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6591</v>
+        <v>6645</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>245.4559918856764</v>
+        <v>255.2783363034538</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>42.05</v>
+        <v>12.65</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>40.52382048289861</v>
+        <v>46.21060650002418</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>26.1134655435874</v>
+        <v>29.50406548288369</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.8932303672744207</v>
+        <v>1.216997632070322</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.08035184606646489</v>
+        <v>0.0822550094043432</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6512</v>
+        <v>6591</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>243.873993092215</v>
+        <v>245.4559918856764</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>20.6</v>
+        <v>42.05</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>52.82939203284421</v>
+        <v>40.52382048289861</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>8.257850989106077</v>
+        <v>26.1134655435874</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.9406990685234714</v>
+        <v>0.8932303672744207</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.3873765839864264</v>
+        <v>0.08035184606646489</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6698</v>
+        <v>6512</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>240.5502182713739</v>
+        <v>243.873993092215</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>31.9</v>
+        <v>20.6</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>47.87644807196565</v>
+        <v>52.82939203284421</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>13.5313820061721</v>
+        <v>8.257850989106077</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.8588392876606594</v>
+        <v>0.9406990685234714</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.1263246986329426</v>
+        <v>0.3873765839864264</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6556</v>
+        <v>6698</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>238.5737489091114</v>
+        <v>240.5502182713739</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>61.3</v>
+        <v>31.9</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>48.25403715484906</v>
+        <v>47.87644807196565</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>10.35401192106885</v>
+        <v>13.5313820061721</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4853196832142167</v>
+        <v>0.8588392876606594</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2179005827569832</v>
+        <v>0.1263246986329426</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6494</v>
+        <v>6556</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>238.2038143075662</v>
+        <v>238.5737489091114</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>49.6</v>
+        <v>61.3</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>35.64132793413935</v>
+        <v>48.25403715484906</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.64962340175287</v>
+        <v>10.35401192106885</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.795941221526491</v>
+        <v>0.4853196832142167</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.5966691301101101</v>
+        <v>0.2179005827569832</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6582</v>
+        <v>6494</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>237.898546020573</v>
+        <v>238.2038143075662</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>31.05</v>
+        <v>49.6</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>35.07747977856002</v>
+        <v>35.64132793413935</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>21.54258174070806</v>
+        <v>15.64962340175287</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.9646687687489748</v>
+        <v>0.795941221526491</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.119740134987854</v>
+        <v>-0.5966691301101101</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6695</v>
+        <v>6582</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>236.4114764392181</v>
+        <v>237.898546020573</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>47.9</v>
+        <v>31.05</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>47.71523709477077</v>
+        <v>35.07747977856002</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9.992040309828536</v>
+        <v>21.54258174070806</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7717490195228149</v>
+        <v>0.9646687687489748</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0371616809358038</v>
+        <v>-0.119740134987854</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6741</v>
+        <v>6695</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>235.2506954573655</v>
+        <v>236.4114764392181</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>58.8</v>
+        <v>47.9</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>52.5388993656839</v>
+        <v>47.71523709477077</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>23.57400266866786</v>
+        <v>9.992040309828536</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4314751752619479</v>
+        <v>0.7717490195228149</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1115444153264872</v>
+        <v>-0.0371616809358038</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6768</v>
+        <v>6741</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>235.2131331855581</v>
+        <v>235.2506954573655</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>62</v>
+        <v>58.8</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>32.80155338197648</v>
+        <v>52.5388993656839</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>30.24651690758112</v>
+        <v>23.57400266866786</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.9557448917517096</v>
+        <v>0.4314751752619479</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0217416190628161</v>
+        <v>-0.1115444153264872</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6823</v>
+        <v>6768</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>227.0395551210705</v>
+        <v>235.2131331855581</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>59.7</v>
+        <v>62</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>43.25525351234432</v>
+        <v>32.80155338197648</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>27.23286942035824</v>
+        <v>30.24651690758112</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5683347393602638</v>
+        <v>0.9557448917517096</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0749478246660548</v>
+        <v>0.0217416190628161</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6708</v>
+        <v>6823</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>223.5878832014793</v>
+        <v>227.0395551210705</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>37.1</v>
+        <v>59.7</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>50.44768014234701</v>
+        <v>43.25525351234432</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>5.798585524333063</v>
+        <v>27.23286942035824</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6924151634636282</v>
+        <v>0.5683347393602638</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.3214167513439063</v>
+        <v>-0.0749478246660548</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6792</v>
+        <v>6708</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>222.161724212122</v>
+        <v>223.5878832014793</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>58.7</v>
+        <v>37.1</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>49.42134224066485</v>
+        <v>50.44768014234701</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15.99017394241336</v>
+        <v>5.798585524333063</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6878913241770412</v>
+        <v>0.6924151634636282</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1553940837558101</v>
+        <v>-0.3214167513439063</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6776</v>
+        <v>6792</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>221.8338338626116</v>
+        <v>222.161724212122</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>52</v>
+        <v>58.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>38.71649479281978</v>
+        <v>49.42134224066485</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>20.51372469467622</v>
+        <v>15.99017394241336</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5319498186739775</v>
+        <v>0.6878913241770412</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0721330528641525</v>
+        <v>-0.1553940837558101</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6561</v>
+        <v>6776</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>218.8980733708943</v>
+        <v>221.8338338626116</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>313</v>
+        <v>52</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.13554899259778</v>
+        <v>38.71649479281978</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.41203442898671</v>
+        <v>20.51372469467622</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8988714051484216</v>
+        <v>0.5319498186739775</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.9302403059939928</v>
+        <v>-0.0721330528641525</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6485</v>
+        <v>6561</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>213.8338936838434</v>
+        <v>218.8980733708943</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>59.8</v>
+        <v>313</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>44.13332591322354</v>
+        <v>39.13554899259778</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>17.9892866834888</v>
+        <v>13.41203442898671</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7019742795055395</v>
+        <v>0.8988714051484216</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>1</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1016168465947824</v>
+        <v>-0.9302403059939928</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6477</v>
+        <v>6485</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>212.3768017246596</v>
+        <v>213.8338936838434</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>33.95</v>
+        <v>59.8</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.65227181965298</v>
+        <v>44.13332591322354</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>11.24898516817104</v>
+        <v>17.9892866834888</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2882645630938059</v>
+        <v>0.7019742795055395</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1884289002455856</v>
+        <v>0.1016168465947824</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6605</v>
+        <v>6477</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>212.1434116402881</v>
+        <v>212.3768017246596</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>136</v>
+        <v>33.95</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.94278012753441</v>
+        <v>42.65227181965298</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>11.92098958143831</v>
+        <v>11.24898516817104</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.7053065613887116</v>
+        <v>0.2882645630938059</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.3310527779413048</v>
+        <v>-0.1884289002455856</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6589</v>
+        <v>6605</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>209.0923004929089</v>
+        <v>212.1434116402881</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>48.95</v>
+        <v>136</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>52.32818816164118</v>
+        <v>46.94278012753441</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>14.6664846928735</v>
+        <v>11.92098958143831</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.139088818167854</v>
+        <v>0.7053065613887116</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0587847430620732</v>
+        <v>-0.3310527779413048</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6720</v>
+        <v>6589</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>201.3049264727097</v>
+        <v>209.0923004929089</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>129.5</v>
+        <v>48.95</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>50.86645393173644</v>
+        <v>52.32818816164118</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>29.11140498955796</v>
+        <v>14.6664846928735</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.10341683648827</v>
+        <v>1.139088818167854</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.6889209492752988</v>
+        <v>-0.0587847430620732</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6803</v>
+        <v>6720</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>188.1667592895753</v>
+        <v>201.3049264727097</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>269</v>
+        <v>129.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>44.90748677766495</v>
+        <v>50.86645393173644</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.36022280235691</v>
+        <v>29.11140498955796</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3722170598033246</v>
+        <v>0.10341683648827</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0150533308668713</v>
+        <v>-0.6889209492752988</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6757</v>
+        <v>6803</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>179.2292220493375</v>
+        <v>188.1667592895753</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>53</v>
+        <v>269</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>34.58087944760831</v>
+        <v>44.90748677766495</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.64449978306715</v>
+        <v>14.36022280235691</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8234391581190214</v>
+        <v>0.3722170598033246</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.2541388676244235</v>
+        <v>0.0150533308668713</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6641</v>
+        <v>6757</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>179.196842171046</v>
+        <v>179.2292220493375</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>16.9</v>
+        <v>53</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>50.95569671881447</v>
+        <v>34.58087944760831</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>12.52815894508211</v>
+        <v>16.64449978306715</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.19882043895491</v>
+        <v>0.8234391581190214</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.3342702890272694</v>
+        <v>-0.2541388676244235</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6732</v>
+        <v>6641</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>176.1992733496009</v>
+        <v>179.196842171046</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>146.5</v>
+        <v>16.9</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>39.15677139821442</v>
+        <v>50.95569671881447</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>21.38027430659108</v>
+        <v>12.52815894508211</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3602825469992367</v>
+        <v>0.19882043895491</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.2629483180488803</v>
+        <v>-0.3342702890272694</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6498</v>
+        <v>6732</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>167.1877239704324</v>
+        <v>176.1992733496009</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>66.2</v>
+        <v>146.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>37.68942115950494</v>
+        <v>39.15677139821442</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.55582406175268</v>
+        <v>21.38027430659108</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5230225914774402</v>
+        <v>0.3602825469992367</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>1</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.7603621632271538</v>
+        <v>0.2629483180488803</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6763</v>
+        <v>6498</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>158.7028716585635</v>
+        <v>167.1877239704324</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>41</v>
+        <v>66.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>42.88950434258481</v>
+        <v>37.68942115950494</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.73872248986</v>
+        <v>18.55582406175268</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5456809984690834</v>
+        <v>0.5230225914774402</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0397836561210149</v>
+        <v>-0.7603621632271538</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6614</v>
+        <v>6763</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>157.0412310788199</v>
+        <v>158.7028716585635</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>35.45</v>
+        <v>41</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.51332307255195</v>
+        <v>42.88950434258481</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>8.774003892163462</v>
+        <v>16.73872248986</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.3960647636844852</v>
+        <v>0.5456809984690834</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.062821013109292</v>
+        <v>0.0397836561210149</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6794</v>
+        <v>6614</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>150.4802863860233</v>
+        <v>157.0412310788199</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>35.45</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>47.97956655260541</v>
+        <v>38.51332307255195</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13.88802662033172</v>
+        <v>8.774003892163462</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6391148968805866</v>
+        <v>0.3960647636844852</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0971155146246663</v>
+        <v>0.062821013109292</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6671</v>
+        <v>6794</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>148.8769348310118</v>
+        <v>150.4802863860233</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>22.85</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46.17472084280992</v>
+        <v>47.97956655260541</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.80585842827984</v>
+        <v>13.88802662033172</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3976044905918937</v>
+        <v>0.6391148968805866</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0014735128390706</v>
+        <v>0.0971155146246663</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6550</v>
+        <v>6671</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>148.3885738188338</v>
+        <v>148.8769348310118</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>9.92</v>
+        <v>22.85</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>35.93313352922944</v>
+        <v>46.17472084280992</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>14.4253104881802</v>
+        <v>13.80585842827984</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5912643743928939</v>
+        <v>0.3976044905918937</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0329445664185563</v>
+        <v>-0.0014735128390706</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6790</v>
+        <v>6550</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>147.9966368913358</v>
+        <v>148.3885738188338</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>37.65</v>
+        <v>9.92</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>35.17568590851552</v>
+        <v>35.93313352922944</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11.8044829273943</v>
+        <v>14.4253104881802</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.111912458050122</v>
+        <v>0.5912643743928939</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0058669891976919</v>
+        <v>-0.0329445664185563</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6546</v>
+        <v>6790</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>129.960158330278</v>
+        <v>147.9966368913358</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>60.2</v>
+        <v>37.65</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>44.00656308128288</v>
+        <v>35.17568590851552</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>15.15033841581465</v>
+        <v>11.8044829273943</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.5380743421548669</v>
+        <v>1.111912458050122</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.3044235449462438</v>
+        <v>-0.0058669891976919</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6592</v>
+        <v>6546</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>121.4502822574261</v>
+        <v>129.960158330278</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>59.6</v>
+        <v>60.2</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>40.00403552746376</v>
+        <v>44.00656308128288</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9.695477355712384</v>
+        <v>15.15033841581465</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.114050789791723</v>
+        <v>0.5380743421548669</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.1282199407366841</v>
+        <v>-0.3044235449462438</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6534</v>
+        <v>6592</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>115.3150715878162</v>
+        <v>121.4502822574261</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>89.8</v>
+        <v>59.6</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>35.85104844447682</v>
+        <v>40.00403552746376</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>11.52616142213624</v>
+        <v>9.695477355712384</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5092735575560462</v>
+        <v>1.114050789791723</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1826450310742503</v>
+        <v>-0.1282199407366841</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6835</v>
+        <v>6534</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>108.6140586856514</v>
+        <v>115.3150715878162</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>30.7</v>
+        <v>89.8</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>44.65330220391992</v>
+        <v>35.85104844447682</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.05480374159802</v>
+        <v>11.52616142213624</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.8352810239287701</v>
+        <v>0.5092735575560462</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0092324530984836</v>
+        <v>-0.1826450310742503</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6625</v>
+        <v>6835</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>105.3991042098739</v>
+        <v>108.6140586856514</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>73.5</v>
+        <v>30.7</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>33.55894632728661</v>
+        <v>44.65330220391992</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>13.84979737546191</v>
+        <v>17.05480374159802</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.3164769496327352</v>
+        <v>0.8352810239287701</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.3366717382696421</v>
+        <v>-0.0092324530984836</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6821</v>
+        <v>6625</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>83.15613526649042</v>
+        <v>105.3991042098739</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>41</v>
+        <v>73.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>46.07723631298756</v>
+        <v>33.55894632728661</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>12.64523410750006</v>
+        <v>13.84979737546191</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.4971927974686079</v>
+        <v>0.3164769496327352</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.1094044192658767</v>
+        <v>-0.3366717382696421</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,52 +7152,105 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>6821</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>聯寶</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>83.15613526649042</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>46.07723631298756</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>12.64523410750006</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.4971927974686079</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.1094044192658767</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>6552</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>易華電</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>82.44029408746312</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E128" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>33.25898531616525</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>17.17393145248319</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J128" s="2" t="n">
         <v>0.4057965155916817</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>-0.0532491276277797</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
